--- a/teste/antosc_registo_mestre_real.xlsx
+++ b/teste/antosc_registo_mestre_real.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joaquim.pedro\Documents\Antosc\teste\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82BE2231-D58D-4F86-919E-7A181DBD4B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A961EB44-C171-487C-B81E-2AB73CA524D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="30915" windowHeight="16876" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,14 @@
     <sheet name="Gaps e Inconsistencias" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registo Mestre'!$A$1:$V$213</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Registo Mestre'!$A$1:$Y$213</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3856" uniqueCount="1160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3873" uniqueCount="1165">
   <si>
     <t>Site ID ANTOSC</t>
   </si>
@@ -3505,6 +3505,21 @@
   </si>
   <si>
     <t>não definido</t>
+  </si>
+  <si>
+    <t>community1;community2</t>
+  </si>
+  <si>
+    <t>latitude</t>
+  </si>
+  <si>
+    <t>longitude</t>
+  </si>
+  <si>
+    <t>enetek</t>
+  </si>
+  <si>
+    <t xml:space="preserve">public </t>
   </si>
 </sst>
 </file>
@@ -3582,7 +3597,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3592,6 +3607,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3894,7 +3910,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W213"/>
+  <dimension ref="A1:Y213"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -3915,9 +3931,10 @@
     <col min="21" max="21" width="8" customWidth="1"/>
     <col min="22" max="22" width="16" customWidth="1"/>
     <col min="23" max="23" width="24.46484375" customWidth="1"/>
+    <col min="24" max="24" width="18.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="27.75" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:25" ht="27.75" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3987,8 +4004,14 @@
       <c r="W1" s="1" t="s">
         <v>1156</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="X1" s="1" t="s">
+        <v>1161</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>22</v>
       </c>
@@ -4052,7 +4075,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>35</v>
       </c>
@@ -4112,7 +4135,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>42</v>
       </c>
@@ -4176,7 +4199,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>50</v>
       </c>
@@ -4226,7 +4249,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>56</v>
       </c>
@@ -4284,7 +4307,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>65</v>
       </c>
@@ -4348,7 +4371,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>72</v>
       </c>
@@ -4412,7 +4435,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A9" s="2" t="s">
         <v>78</v>
       </c>
@@ -4477,8 +4500,11 @@
       <c r="V9" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="W9" s="6" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>85</v>
       </c>
@@ -4542,7 +4568,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A11" s="2" t="s">
         <v>93</v>
       </c>
@@ -4608,7 +4634,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A12" s="3" t="s">
         <v>99</v>
       </c>
@@ -4662,7 +4688,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A13" s="2" t="s">
         <v>102</v>
       </c>
@@ -4728,7 +4754,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A14" s="2" t="s">
         <v>108</v>
       </c>
@@ -4794,7 +4820,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A15" s="2" t="s">
         <v>114</v>
       </c>
@@ -4852,7 +4878,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
         <v>119</v>
       </c>
@@ -4916,6 +4942,9 @@
       <c r="U16" s="2"/>
       <c r="V16" s="2" t="s">
         <v>32</v>
+      </c>
+      <c r="W16" t="s">
+        <v>1160</v>
       </c>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.45">
@@ -5225,7 +5254,7 @@
       </c>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="6" t="s">
         <v>147</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -6405,6 +6434,9 @@
       <c r="V40" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="W40" s="6" t="s">
+        <v>1157</v>
+      </c>
     </row>
     <row r="41" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A41" s="2" t="s">
@@ -7659,6 +7691,9 @@
       <c r="V60" s="2" t="s">
         <v>32</v>
       </c>
+      <c r="W60" t="s">
+        <v>1160</v>
+      </c>
     </row>
     <row r="61" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A61" s="2" t="s">
@@ -7917,7 +7952,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A65" s="3" t="s">
         <v>377</v>
       </c>
@@ -7965,7 +8000,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
         <v>379</v>
       </c>
@@ -8029,7 +8064,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A67" s="2" t="s">
         <v>385</v>
       </c>
@@ -8091,7 +8126,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
         <v>390</v>
       </c>
@@ -8155,7 +8190,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A69" s="2" t="s">
         <v>395</v>
       </c>
@@ -8219,7 +8254,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A70" s="2" t="s">
         <v>401</v>
       </c>
@@ -8283,7 +8318,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A71" s="2" t="s">
         <v>406</v>
       </c>
@@ -8339,7 +8374,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A72" s="2" t="s">
         <v>411</v>
       </c>
@@ -8403,7 +8438,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A73" s="2" t="s">
         <v>416</v>
       </c>
@@ -8467,7 +8502,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A74" s="2" t="s">
         <v>423</v>
       </c>
@@ -8533,7 +8568,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A75" s="2" t="s">
         <v>428</v>
       </c>
@@ -8599,7 +8634,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A76" s="3" t="s">
         <v>433</v>
       </c>
@@ -8649,7 +8684,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="77" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A77" s="2" t="s">
         <v>436</v>
       </c>
@@ -8707,7 +8742,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A78" s="3" t="s">
         <v>441</v>
       </c>
@@ -8757,7 +8792,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A79" s="2" t="s">
         <v>443</v>
       </c>
@@ -8820,8 +8855,11 @@
       <c r="V79" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="80" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="W79" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="80" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A80" s="2" t="s">
         <v>448</v>
       </c>
@@ -8885,7 +8923,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A81" s="2" t="s">
         <v>454</v>
       </c>
@@ -8949,7 +8987,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A82" s="2" t="s">
         <v>459</v>
       </c>
@@ -9013,7 +9051,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A83" s="2" t="s">
         <v>465</v>
       </c>
@@ -9077,7 +9115,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A84" s="2" t="s">
         <v>471</v>
       </c>
@@ -9141,7 +9179,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A85" s="2" t="s">
         <v>477</v>
       </c>
@@ -9204,8 +9242,11 @@
       <c r="V85" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="W85" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A86" s="2" t="s">
         <v>482</v>
       </c>
@@ -9269,7 +9310,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A87" s="2" t="s">
         <v>488</v>
       </c>
@@ -9335,7 +9376,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A88" s="2" t="s">
         <v>493</v>
       </c>
@@ -9393,7 +9434,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A89" s="3" t="s">
         <v>500</v>
       </c>
@@ -9443,7 +9484,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A90" s="2" t="s">
         <v>502</v>
       </c>
@@ -9505,7 +9546,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A91" s="2" t="s">
         <v>508</v>
       </c>
@@ -9567,7 +9608,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A92" s="2" t="s">
         <v>513</v>
       </c>
@@ -9629,7 +9670,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A93" s="2" t="s">
         <v>518</v>
       </c>
@@ -9693,7 +9734,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A94" s="2" t="s">
         <v>524</v>
       </c>
@@ -9757,7 +9798,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A95" s="2" t="s">
         <v>530</v>
       </c>
@@ -9813,7 +9854,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A96" s="2" t="s">
         <v>535</v>
       </c>
@@ -9873,7 +9914,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="97" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A97" s="3" t="s">
         <v>540</v>
       </c>
@@ -9925,7 +9966,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A98" s="3" t="s">
         <v>544</v>
       </c>
@@ -9979,7 +10020,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="99" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A99" s="2" t="s">
         <v>548</v>
       </c>
@@ -10039,7 +10080,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="100" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A100" s="3" t="s">
         <v>553</v>
       </c>
@@ -10091,7 +10132,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="101" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A101" s="2" t="s">
         <v>555</v>
       </c>
@@ -10155,7 +10196,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="102" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A102" s="2" t="s">
         <v>560</v>
       </c>
@@ -10211,7 +10252,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="103" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A103" s="2" t="s">
         <v>566</v>
       </c>
@@ -10267,7 +10308,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="104" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A104" s="2" t="s">
         <v>571</v>
       </c>
@@ -10330,8 +10371,11 @@
       <c r="V104" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="105" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="W104" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="105" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A105" s="3" t="s">
         <v>577</v>
       </c>
@@ -10385,7 +10429,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="106" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A106" s="2" t="s">
         <v>579</v>
       </c>
@@ -10447,7 +10491,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="107" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A107" s="2" t="s">
         <v>584</v>
       </c>
@@ -10505,7 +10549,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="108" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A108" s="2" t="s">
         <v>589</v>
       </c>
@@ -10569,7 +10613,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="109" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A109" s="2" t="s">
         <v>594</v>
       </c>
@@ -10633,7 +10677,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="110" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A110" s="2" t="s">
         <v>599</v>
       </c>
@@ -10689,7 +10733,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="111" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A111" s="2" t="s">
         <v>604</v>
       </c>
@@ -10753,7 +10797,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="112" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A112" s="2" t="s">
         <v>609</v>
       </c>
@@ -10811,7 +10855,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="113" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A113" s="2" t="s">
         <v>615</v>
       </c>
@@ -10877,7 +10921,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="114" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A114" s="2" t="s">
         <v>620</v>
       </c>
@@ -10939,7 +10983,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="115" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A115" s="2" t="s">
         <v>626</v>
       </c>
@@ -10993,7 +11037,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="116" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A116" s="3" t="s">
         <v>631</v>
       </c>
@@ -11041,7 +11085,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="117" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A117" s="2" t="s">
         <v>634</v>
       </c>
@@ -11105,7 +11149,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="118" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A118" s="3" t="s">
         <v>639</v>
       </c>
@@ -11155,7 +11199,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="119" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A119" s="2" t="s">
         <v>641</v>
       </c>
@@ -11211,7 +11255,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="120" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A120" s="2" t="s">
         <v>646</v>
       </c>
@@ -11273,7 +11317,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="121" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A121" s="3" t="s">
         <v>654</v>
       </c>
@@ -11323,7 +11367,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="122" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A122" s="2" t="s">
         <v>656</v>
       </c>
@@ -11387,8 +11431,8 @@
         <v>32</v>
       </c>
     </row>
-    <row r="123" spans="1:22" x14ac:dyDescent="0.45">
-      <c r="A123" s="2" t="s">
+    <row r="123" spans="1:23" x14ac:dyDescent="0.45">
+      <c r="A123" s="6" t="s">
         <v>663</v>
       </c>
       <c r="B123" s="2" t="s">
@@ -11412,8 +11456,8 @@
       <c r="H123" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="I123" s="2" t="s">
-        <v>161</v>
+      <c r="I123" s="6" t="s">
+        <v>1163</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>667</v>
@@ -11449,7 +11493,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="124" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A124" s="2" t="s">
         <v>669</v>
       </c>
@@ -11511,7 +11555,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="125" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A125" s="3" t="s">
         <v>674</v>
       </c>
@@ -11563,7 +11607,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="126" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A126" s="2" t="s">
         <v>676</v>
       </c>
@@ -11623,7 +11667,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="127" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A127" s="2" t="s">
         <v>681</v>
       </c>
@@ -11688,8 +11732,11 @@
       <c r="V127" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="128" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="W127" s="6" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="128" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A128" s="2" t="s">
         <v>685</v>
       </c>
@@ -12729,7 +12776,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="145" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A145" s="2" t="s">
         <v>774</v>
       </c>
@@ -12795,7 +12842,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="146" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A146" s="2" t="s">
         <v>779</v>
       </c>
@@ -12859,7 +12906,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="147" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A147" s="2" t="s">
         <v>784</v>
       </c>
@@ -12923,7 +12970,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="148" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A148" s="2" t="s">
         <v>789</v>
       </c>
@@ -12987,7 +13034,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="149" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A149" s="3" t="s">
         <v>794</v>
       </c>
@@ -13043,7 +13090,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="150" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A150" s="3" t="s">
         <v>798</v>
       </c>
@@ -13097,7 +13144,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="151" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A151" s="2" t="s">
         <v>801</v>
       </c>
@@ -13160,8 +13207,11 @@
       <c r="V151" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="152" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="W151" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="152" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A152" s="2" t="s">
         <v>806</v>
       </c>
@@ -13225,7 +13275,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="153" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A153" s="2" t="s">
         <v>812</v>
       </c>
@@ -13291,7 +13341,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="154" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A154" s="2" t="s">
         <v>818</v>
       </c>
@@ -13357,7 +13407,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="155" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A155" s="2" t="s">
         <v>823</v>
       </c>
@@ -13421,7 +13471,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="156" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A156" s="3" t="s">
         <v>828</v>
       </c>
@@ -13471,7 +13521,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="157" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A157" s="2" t="s">
         <v>830</v>
       </c>
@@ -13537,7 +13587,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="158" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A158" s="2" t="s">
         <v>835</v>
       </c>
@@ -13593,7 +13643,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="159" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A159" s="2" t="s">
         <v>840</v>
       </c>
@@ -13657,14 +13707,14 @@
         <v>32</v>
       </c>
     </row>
-    <row r="160" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A160" s="2" t="s">
         <v>845</v>
       </c>
       <c r="B160" s="2" t="s">
         <v>846</v>
       </c>
-      <c r="C160" s="2" t="s">
+      <c r="C160" s="6" t="s">
         <v>847</v>
       </c>
       <c r="D160" s="2" t="s">
@@ -13721,7 +13771,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="161" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A161" s="2" t="s">
         <v>851</v>
       </c>
@@ -13785,7 +13835,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="162" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A162" s="2" t="s">
         <v>856</v>
       </c>
@@ -13851,7 +13901,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="163" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A163" s="2" t="s">
         <v>861</v>
       </c>
@@ -13915,7 +13965,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="164" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A164" s="2" t="s">
         <v>866</v>
       </c>
@@ -13981,7 +14031,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="165" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A165" s="2" t="s">
         <v>871</v>
       </c>
@@ -14043,7 +14093,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="166" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A166" s="3" t="s">
         <v>877</v>
       </c>
@@ -14095,7 +14145,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="167" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A167" s="2" t="s">
         <v>879</v>
       </c>
@@ -14159,7 +14209,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="168" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A168" s="2" t="s">
         <v>884</v>
       </c>
@@ -14221,7 +14271,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="169" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A169" s="2" t="s">
         <v>889</v>
       </c>
@@ -14279,7 +14329,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="170" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A170" s="2" t="s">
         <v>894</v>
       </c>
@@ -14343,7 +14393,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="171" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A171" s="2" t="s">
         <v>899</v>
       </c>
@@ -14405,7 +14455,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="172" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A172" s="2" t="s">
         <v>904</v>
       </c>
@@ -14470,8 +14520,11 @@
       <c r="V172" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="173" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="W172" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="173" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A173" s="2" t="s">
         <v>909</v>
       </c>
@@ -14535,7 +14588,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="174" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A174" s="2" t="s">
         <v>915</v>
       </c>
@@ -14598,8 +14651,11 @@
       <c r="V174" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="175" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="W174" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="175" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A175" s="2" t="s">
         <v>921</v>
       </c>
@@ -14663,7 +14719,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="176" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A176" s="2" t="s">
         <v>927</v>
       </c>
@@ -14726,8 +14782,11 @@
       <c r="V176" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="177" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="W176" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="177" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A177" s="2" t="s">
         <v>932</v>
       </c>
@@ -14783,7 +14842,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="178" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A178" s="2" t="s">
         <v>937</v>
       </c>
@@ -14847,7 +14906,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="179" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A179" s="2" t="s">
         <v>942</v>
       </c>
@@ -14913,7 +14972,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="180" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A180" s="2" t="s">
         <v>949</v>
       </c>
@@ -14976,8 +15035,11 @@
       <c r="V180" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="181" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="W180" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="181" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A181" s="2" t="s">
         <v>954</v>
       </c>
@@ -15039,7 +15101,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="182" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A182" s="2" t="s">
         <v>958</v>
       </c>
@@ -15103,7 +15165,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="183" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A183" s="2" t="s">
         <v>964</v>
       </c>
@@ -15167,7 +15229,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="184" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A184" s="3" t="s">
         <v>969</v>
       </c>
@@ -15221,7 +15283,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="185" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A185" s="2" t="s">
         <v>971</v>
       </c>
@@ -15281,7 +15343,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="186" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A186" s="2" t="s">
         <v>976</v>
       </c>
@@ -15347,7 +15409,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="187" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A187" s="2" t="s">
         <v>983</v>
       </c>
@@ -15409,7 +15471,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="188" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A188" s="2" t="s">
         <v>988</v>
       </c>
@@ -15471,7 +15533,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="189" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A189" s="2" t="s">
         <v>993</v>
       </c>
@@ -15537,7 +15599,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="190" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A190" s="2" t="s">
         <v>998</v>
       </c>
@@ -15597,7 +15659,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="191" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A191" s="2" t="s">
         <v>1003</v>
       </c>
@@ -15660,8 +15722,11 @@
       <c r="V191" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="192" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="W191" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="192" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A192" s="3" t="s">
         <v>1008</v>
       </c>
@@ -16569,7 +16634,7 @@
       <c r="I207" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="J207" s="3" t="s">
+      <c r="J207" s="7" t="s">
         <v>1074</v>
       </c>
       <c r="K207" s="3"/>
@@ -16657,7 +16722,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="209" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A209" s="2" t="s">
         <v>1082</v>
       </c>
@@ -16721,7 +16786,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="210" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A210" s="2" t="s">
         <v>1087</v>
       </c>
@@ -16779,7 +16844,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="211" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A211" s="2" t="s">
         <v>1092</v>
       </c>
@@ -16845,7 +16910,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="212" spans="1:22" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A212" s="2" t="s">
         <v>1098</v>
       </c>
@@ -16906,8 +16971,11 @@
       <c r="V212" s="2" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="213" spans="1:22" x14ac:dyDescent="0.45">
+      <c r="W212" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="213" spans="1:23" x14ac:dyDescent="0.45">
       <c r="A213" s="2" t="s">
         <v>1103</v>
       </c>
@@ -16966,7 +17034,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V213" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
